--- a/www/download/COUNTRY.ROU.WIOD13.xlsx
+++ b/www/download/COUNTRY.ROU.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Romênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.200944842620698</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.30565803346184</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.707018579958228</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.882526813020703</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1.50713623441745</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.14389846899757</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2.89620026258149</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3.30480173923261</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3.31928164503775</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3.25701079222564</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2.91002210893393</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2.80465564467292</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2.43463024937312</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>2.49929403971849</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3.04146434603597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.503</t>
+          <t>0.441133148850499</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.379</t>
+          <t>0.463043218266963</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.023</t>
+          <t>0.545313972306213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.813</t>
+          <t>0.33149771846775</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>0.00722467691286122</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.771</t>
+          <t>-0.0639261328650371</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.657</t>
+          <t>-0.058783418756988</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>0.237274789612572</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.569</t>
+          <t>0.580245306595283</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>0.467363338651781</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.267</t>
+          <t>0.317876904986773</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>0.367181293317905</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>9.365</t>
+          <t>0.328300448454468</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9.366</t>
+          <t>0.273606256382209</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9.212</t>
+          <t>0.404610378670845</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>0.985783588201604</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.894</t>
+          <t>1.0910210665077</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.399</t>
+          <t>1.26012547711603</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5.182</t>
+          <t>0.867856713022716</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.971</t>
+          <t>0.796580783039258</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.882</t>
+          <t>0.561603393052432</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.787</t>
+          <t>0.51628002303329</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.138</t>
+          <t>1.07557647947669</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>1.87118263324307</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6.407</t>
+          <t>1.48773885149996</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>1.24405940925747</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>1.34092158042089</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>1.21754722847264</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6.513</t>
+          <t>1.10782231317466</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6.583</t>
+          <t>1.36049324827756</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17008.077</t>
+          <t>1.78438275767087</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17598.162</t>
+          <t>1.84396269892741</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16800.278</t>
+          <t>2.20804436329515</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16391.695</t>
+          <t>1.48340086931967</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20083.159</t>
+          <t>1.63288333003187</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19959.764</t>
+          <t>1.24525649690655</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19742.438</t>
+          <t>1.04913255275747</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17876.156</t>
+          <t>1.74793102147507</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17579.559</t>
+          <t>1.36559488803569</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17371.251</t>
+          <t>2.35291275489897</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>17171.308</t>
+          <t>1.91663870990645</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17305.201</t>
+          <t>2.14202524300663</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17588.497</t>
+          <t>1.95170760270574</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17593.169</t>
+          <t>1.74270927970021</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17338.698</t>
+          <t>2.1382147084258</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11128.807</t>
+          <t>27817305667.5829</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11394.243</t>
+          <t>29240751764.232</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10468.573</t>
+          <t>26006267060.8688</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10026.345</t>
+          <t>23888540761.159</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11606.427</t>
+          <t>29918736054.63</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11478.276</t>
+          <t>28410884248.3875</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11318.912</t>
+          <t>28127877732.7871</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11929.299</t>
+          <t>24350255856.6951</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11555.4</t>
+          <t>23938064123.7473</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12477.476</t>
+          <t>22931495184.6194</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11991.971</t>
+          <t>22518033528.0188</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12430.286</t>
+          <t>22465052200.889</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>12497.741</t>
+          <t>22845575968.3987</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>12629.99</t>
+          <t>22946159760.4152</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12762.814</t>
+          <t>21824131382.9488</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>4555943491.0419</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>4544852988.26497</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>3742081544.03276</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>4493381146.06479</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>5249201799.807</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>6012498855.33855</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>6343714846.54533</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>5012775393.58699</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>4986649157.08499</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>4453194634.70144</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>4901011248.92804</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>4801732239.74897</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>5100182078.15977</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>5536502720.07461</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>5000625464.22793</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>9766449.18109688</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>9325732.77799318</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>9067101.0872616</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>8147526.32733111</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>10411695.4362851</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>9503841.55375746</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>8380055.86663338</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>7211006.81922847</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>5677578.18784656</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>4209105.16199111</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>3439152.1802336</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>2917235.04468153</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2193837.16675333</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1841840.90633039</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>2214503.23103496</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>109146.706415406</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>112357.927107829</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>105756.416381103</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>101531.579344478</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>127152.155964851</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>130436.14724932</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>125358.862329208</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>112120.930787506</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>118776.931598696</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>123536.084752247</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>130627.959241923</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>136961.60947592</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>155420.946553022</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>172158.362706065</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>156031.835939284</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>216565.320438449</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>229339.743971805</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>202661.274363581</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>185137.105172297</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>236906.264511618</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>234070.69337979</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>225666.599338366</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>199717.761240696</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>211485.505238291</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>223267.691493959</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>234807.483281508</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>245513.66740045</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>282454.098403047</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>314085.198789581</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>278648.322286676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>1.44270094918391</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>1.50706528327688</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>1.79752670657526</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1.2313586834088</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>1.21108416910677</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.909069136837895</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.784271877567775</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>1.37977927661821</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>1.3172674948632</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>1.80191570850497</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>1.44683604891193</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>1.58870869497918</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>1.450449965996</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>1.28122167342307</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>1.55224345940455</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>8617.41287898989</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>9222.91154416165</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>9065.44524486267</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>10087.1150114193</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>10124.3879281573</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>9723.90147694129</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>10710.8418814459</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>11991.5227333167</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>15130.2800767773</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>18727.5018529183</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>23700.9675473141</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>29212.0821964871</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>39496.4662427948</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>46165.9585158812</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>39093.442073649</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.200944842620698</t>
+          <t>783.601618659904</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.30565803346184</t>
+          <t>771.096833803003</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.707018579958228</t>
+          <t>693.082949278516</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.882526813020703</t>
+          <t>867.163662597945</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.50713623441745</t>
+          <t>879.116027433762</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.14389846899757</t>
+          <t>1022.27303499763</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.89620026258149</t>
+          <t>1096.25777153565</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.30480173923261</t>
+          <t>816.718867586716</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.31928164503775</t>
+          <t>845.15179856702</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.25701079222564</t>
+          <t>694.997211814505</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.91002210893393</t>
+          <t>795.334661148298</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.80465564467292</t>
+          <t>748.913257182134</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.43463024937312</t>
+          <t>792.384382530843</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.49929403971849</t>
+          <t>850.069510221805</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.04146434603597</t>
+          <t>759.617060185622</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-2062445329.52594</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-2239074384.57202</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-2307994387.979</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-1935706670.18592</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-2964976166.80031</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-2653432020.0364</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-2449514848.60858</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2627088599.14105</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2317031137.12101</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-1994373037.77551</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>-1751862944.6393</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-1572823768.857</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-1705867682.10049</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>-1765876976.77929</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-1359698702.99982</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2065358371.0676</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2232299708.61044</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2331738060.15283</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-1984149672.67322</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-3050615133.15351</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2751923679.56003</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>-2567383531.63587</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-2788684876.298</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-2553606943.62631</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>-2224868712.52567</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>-2027580729.81451</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1955836785.44862</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-2072443925.00074</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2242736786.42401</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-1874824356.02847</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>2913041.54165705</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>-6774675.96157778</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>23743672.1738312</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>48443002.4873006</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>85638966.3531954</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>98491659.5236303</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>117868683.02729</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>161596277.156948</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>236575806.505303</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>230495674.750159</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>275717785.175206</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>383013016.591624</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>366576242.900243</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>476859809.644718</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>515125653.028654</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1914.1044176826</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1933.19010207223</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1938.9180604786</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1934.9531684745</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1943.79953106682</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1951.58990053558</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1956.02191231617</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1943.61063590596</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>1958.44279104452</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1947.32360515021</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1946.05351984681</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>1938.71826065257</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>1941.69828322846</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>1939.19699063412</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>1938.72767351087</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1789.74356910034</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1876.36006753452</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1862.02344960204</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1860.05019838541</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1850.06162831402</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1853.03340327163</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1852.46288963537</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1867.1564654272</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1837.04049323371</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1846.00231663514</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1852.89221240275</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1854.59232665309</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1878.12971841664</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>1878.34780009182</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1882.18714064088</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>9015.42516999499</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>9424.89168999499</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>54.53</t>
+          <t>9716.80211999499</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>9329.596589995</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>9671.49620999501</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>11602.476589995</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>12503.776749996</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>14965.508649996</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>18960.547039996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>25567.907739996</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31153.799929996</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>38170.103819996</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>32.82</t>
+          <t>48894.796309996</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>60280.244599996</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>46893.386289996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>98.57</t>
+          <t>3144229747.01198</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>109.1</t>
+          <t>3247377448.33035</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>3165858408.47671</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>2773508644.0325</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>3966134633.49363</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>3923868953.95412</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>3828952584.42291</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>107.54</t>
+          <t>4112326693.29412</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>187.11</t>
+          <t>4016037439.94381</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>148.78</t>
+          <t>4021458396.18439</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>3765182235.97388</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>134.05</t>
+          <t>3770130759.49132</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>3507014748.42528</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>110.81</t>
+          <t>3756392937.62042</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>136.05</t>
+          <t>3508556146.93993</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>178.43</t>
+          <t>10941.0688131599</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>184.39</t>
+          <t>12150.2883833094</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>220.8</t>
+          <t>11887.9487200439</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>148.34</t>
+          <t>12425.0202418549</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>164.91</t>
+          <t>11308.9760301437</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>124.52</t>
+          <t>13620.5575021578</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>104.91</t>
+          <t>15604.343044409</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>174.78</t>
+          <t>17610.5644620268</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>136.55</t>
+          <t>23491.8781941283</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>235.29</t>
+          <t>32323.2803527197</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>41395.4874568987</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>214.15</t>
+          <t>52856.4065527493</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>195.14</t>
+          <t>71798.6577295149</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>174.31</t>
+          <t>86273.899594741</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>213.82</t>
+          <t>56842.500007713</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17008.077</t>
+          <t>1379100513.71165</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17598.162</t>
+          <t>1412249144.27637</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16800.278</t>
+          <t>1154967515.87906</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16391.695</t>
+          <t>1283720865.4847</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20083.159</t>
+          <t>1247420076.20702</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19959.764</t>
+          <t>1570017062.19952</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19742.438</t>
+          <t>1863366889.50611</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17876.156</t>
+          <t>1893438900.98796</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17579.559</t>
+          <t>2358843417.47991</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17371.251</t>
+          <t>2929200302.16286</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17171.308</t>
+          <t>3280999845.29765</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17305.201</t>
+          <t>3855459521.18348</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>17588.497</t>
+          <t>4080853972.21449</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>17593.169</t>
+          <t>4280626080.03242</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>17338.698</t>
+          <t>3112730774.50958</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11128.807</t>
+          <t>-1925.6436431649</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11394.243</t>
+          <t>-2725.39669331438</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10468.573</t>
+          <t>-2171.14660004895</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10026.345</t>
+          <t>-3095.4236518599</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11606.427</t>
+          <t>-1637.47982014866</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11478.276</t>
+          <t>-2018.08091216285</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11318.912</t>
+          <t>-3100.56629441306</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11929.299</t>
+          <t>-2645.05581203082</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11555.4</t>
+          <t>-4531.33115413229</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12477.476</t>
+          <t>-6755.37261272371</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11991.971</t>
+          <t>-10241.6875269028</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>12430.286</t>
+          <t>-14686.3027327534</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>12497.741</t>
+          <t>-22903.8614195189</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>12629.99</t>
+          <t>-25993.654994745</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>12762.814</t>
+          <t>-9949.11371771708</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27818.61</t>
+          <t>1765129233.30032</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29241.6</t>
+          <t>1835128304.05397</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26007.069</t>
+          <t>2010890892.59766</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23888.336</t>
+          <t>1489787778.5478</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29615.804</t>
+          <t>2718714557.28662</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>28411.426</t>
+          <t>2353851891.7546</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28129.143</t>
+          <t>1965585694.91681</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24352.118</t>
+          <t>2218887792.30615</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23938.64</t>
+          <t>1657194022.4639</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>22931.339</t>
+          <t>1092258094.02153</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22518.951</t>
+          <t>484182390.676228</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>22468.197</t>
+          <t>-85328761.6921578</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>22848.388</t>
+          <t>-573839223.789207</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>22944.689</t>
+          <t>-524233142.412004</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>21825.005</t>
+          <t>395825372.430355</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>23336.75252</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>23380.70425</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>21982.16619</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>22614.83698</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>19009.69485</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>19167.23233</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>22411.43356</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>25121.62818</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>31505.19079</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>41573.58063</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>51146.00313</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>62791.13112</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>86627.44546</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>107462.62559</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>86061.9317</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14019.638</t>
+          <t>0.046918545764877</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14325.604</t>
+          <t>0.0372294570121809</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13571.066</t>
+          <t>0.0511519184531028</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13100.784</t>
+          <t>0.0136782210536551</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>16057.962</t>
+          <t>0.0258684835715244</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15831.996</t>
+          <t>0.0137885056317101</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15625.169</t>
+          <t>-0.00700984390974683</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13670.158</t>
+          <t>0.00137710939421777</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>13444.372</t>
+          <t>-0.00113092020460888</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12688.209</t>
+          <t>0.0486477261203395</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12527.219</t>
+          <t>0.0245122021385974</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>12532.295</t>
+          <t>0.0265332069654658</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12570.825</t>
+          <t>0.0370998489156647</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12577.394</t>
+          <t>0.0306424268437196</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12220.634</t>
+          <t>0.0335029182238511</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>14284.517009183</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>14117.410760155</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>11690.0745960578</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>16021.0430218163</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>12696.4634033637</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>14925.8000167552</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>16857.3288552141</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>18209.382789563</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>22301.843613053</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>28061.4360667414</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>38830.2546278648</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>47134.0930612798</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>66514.4530613812</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>86485.0219131855</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>66985.0361892292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4556.109</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4544.977</t>
+          <t>20827.7154125453</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3742.185</t>
+          <t>17878.2323324753</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4493.324</t>
+          <t>25574.5068786929</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5216.98</t>
+          <t>19246.946945127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6012.619</t>
+          <t>22387.8492687505</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6343.908</t>
+          <t>26932.9122035333</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5013.093</t>
+          <t>29223.1540073207</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4986.8</t>
+          <t>38004.1607531317</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4453.149</t>
+          <t>37815.7515167356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4901.182</t>
+          <t>56716.3153914071</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4802.552</t>
+          <t>70036.737127413</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>5100.749</t>
+          <t>94380.2326877114</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>5535.76</t>
+          <t>120176.419878924</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5000.694</t>
+          <t>91760.5600450726</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>144.26</t>
+          <t>134405.670555828</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>138291.398437762</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>179.74</t>
+          <t>128341.58407335</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>123.14</t>
+          <t>140767.682605421</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>122.47</t>
+          <t>125102.10611178</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>131661.510884344</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>78.42</t>
+          <t>143033.378187658</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>137.96</t>
+          <t>157317.857442779</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>131.72</t>
+          <t>193740.910292466</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>180.19</t>
+          <t>232061.861481868</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>144.68</t>
+          <t>297438.897168626</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>158.83</t>
+          <t>348189.400856234</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>145.02</t>
+          <t>469596.611271851</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>128.15</t>
+          <t>558820.926701643</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>155.22</t>
+          <t>489307.462464804</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9.767</t>
+          <t>20953.9757959775</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.326</t>
+          <t>21595.0366867756</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.067</t>
+          <t>18568.8891500682</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8.147</t>
+          <t>22952.3748023089</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.194</t>
+          <t>20618.1891217812</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.504</t>
+          <t>23217.9821996451</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.381</t>
+          <t>27580.3621459438</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>7.212</t>
+          <t>27991.1338055133</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5.678</t>
+          <t>29848.6267121628</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4.209</t>
+          <t>24378.2663766318</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.439</t>
+          <t>31500.6716348722</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>34498.1691028764</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.194</t>
+          <t>35897.1168923718</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>39692.5976931957</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>34014.9487228104</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>14284.517009183</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14761.3062974795</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12169.3016784859</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>13975.4343761728</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12548.8282212418</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>14549.9339435519</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16120.6752889863</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>15916.0977565602</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16058.847195775</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>17122.527383603</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>19040.4391163132</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>20032.3729149732</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>21698.0059961549</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>24743.7870455706</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>21639.7454171529</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14923.5314840225</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>14371.4252174547</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15630.3634875247</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>12012.5664913071</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>13360.589704873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>11539.3169612495</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9708.20022646666</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>12208.1666326793</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>14911.1745668683</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>30016.7837332644</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>30991.8499185929</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>38450.663632587</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>56918.4295722886</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>63289.5878810759</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>55486.6699749274</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>11128807489.9963</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>11394243144.4763</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10468573057.614</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10026345038.1371</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>11606427000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11478276000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11318912000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11929299000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11555400000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>12477476000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>11991971000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>12430286000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>12497741000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>12629990000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>12762813634.0076</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>17008076566.2517</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>17598162191.4035</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16800278404.2581</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>16391695466.7451</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20083159000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>19959764000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>19742438000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>17876156000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>17579559000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>17371251000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17171308000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>17305201000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>17588497000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>17593169000</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>17338697861.6088</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14019637533.9338</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>14325603571.388</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13571066383.7692</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13100784250.9917</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>16057962000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15831996000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15625169000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13670158000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13444372000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12688209000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12527219000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12532295000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12570825000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12577394000</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12220634452.4776</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9503080.13946449</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9378883.34754797</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9022592.28144989</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8812501.66311301</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10855400</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10771400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10657400</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9574000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9569500</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9410200</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9267300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>9331000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>9364900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>9366300</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>9211994.64560414</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5814106.78915309</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5894010.69882498</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>5399182.80766852</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5181699.07235622</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5971000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5881500</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5786700</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6137700</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5900300</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6407500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6162200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>6411600</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6436500</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6513000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6583087.35589215</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>17008076566.2517</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>17598162191.4035</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16800278404.2581</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>16391695466.7451</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20083159000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>19959764000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>19742438000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>17876156000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17579559000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17371251000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17171308000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17305201000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>17588497000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>17593169000</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>17338697861.6088</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>11128807489.9963</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11394243144.4763</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10468573057.614</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10026345038.1371</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>11606427000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11478276000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11318912000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11929299000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>11555400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>12477476000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>11991971000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>12430286000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>12497741000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>12629990000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>12762813634.0076</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>79644.24419</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>82950.2155</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>76895.00852</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>80843.09454</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>72237.66396</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>73192.59749</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>78998.85387</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>89452.53788</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>115044.05127</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>148577.15376</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>188278.39696</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>234079.32454</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>322023.23116</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>394379.72946</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>312861.4044</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>35877.50728</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>35199.14063</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>33508.59582</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>37587.07337</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>32607.53665</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>33927.16623</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>36641.11243</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>41431.32064</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>52915.33532</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>67832.53525</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>87708.16531</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>108487.40076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>151298.66226</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>183466.00776</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>147247.23002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>27008.1262578989</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>27560.7777695561</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>28102.593183816</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>28512.4330760852</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>28817.1042268573</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29192.1470307955</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>29694.9838785975</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30317.3124995246</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31062.735151797</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>31986.3200668522</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33198.7943111179</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34855.640122582</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>37358.6348316571</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>40334.0438289789</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>41909.9936147802</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
